--- a/data/03-21-densitycutter.xlsx
+++ b/data/03-21-densitycutter.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/819f14cd63a8f0d1/Masterarbeit-Jil_Lehnert/03-21-Messung/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jille\Documents\Uni\Master-Mechatronik\Masterarbeit\SMP-SignalProcessing\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="20" documentId="8_{B278DC17-B06E-4616-908E-B45A7AA114B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B122E6FD-0CA8-4E32-B9FE-5FBD56860DAB}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0879BE1A-EB3F-46B4-9BE2-7429CEE3B3FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{FC14D368-F54E-477D-9C66-9A96069A1AC9}"/>
+    <workbookView xWindow="-28905" yWindow="60" windowWidth="14610" windowHeight="15585" xr2:uid="{FC14D368-F54E-477D-9C66-9A96069A1AC9}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,23 +36,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="11">
   <si>
     <t>snowdepth</t>
   </si>
   <si>
-    <t>---</t>
-  </si>
-  <si>
-    <t>----</t>
-  </si>
-  <si>
     <t>snowheight</t>
   </si>
   <si>
-    <t>density1 in kg/m^3</t>
-  </si>
-  <si>
     <t>density2</t>
   </si>
   <si>
@@ -65,10 +56,19 @@
     <t>deviation 2</t>
   </si>
   <si>
-    <t>mean</t>
-  </si>
-  <si>
     <t>Nan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mean </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> in kg/m^3</t>
+  </si>
+  <si>
+    <t>density1</t>
+  </si>
+  <si>
+    <t>density4</t>
   </si>
 </sst>
 </file>
@@ -115,7 +115,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -455,36 +455,42 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{048771F2-3FA2-40BD-AAEC-D8ABA50D1216}">
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" t="s">
+      <c r="F1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" t="s">
         <v>4</v>
       </c>
-      <c r="D1" t="s">
+      <c r="H1" t="s">
         <v>5</v>
       </c>
-      <c r="E1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="G1" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="H1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" s="3">
         <v>3.5</v>
       </c>
@@ -492,18 +498,18 @@
         <v>85</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
-      <c r="F2" t="s">
-        <v>10</v>
-      </c>
-      <c r="H2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="G2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
         <v>8.5</v>
       </c>
@@ -519,20 +525,20 @@
       <c r="E3" s="1">
         <v>174</v>
       </c>
-      <c r="F3">
-        <f t="shared" ref="F3:F12" si="0">ABS(D3 - C3) / C3 * 100</f>
+      <c r="G3">
+        <f>ABS(D3 - C3) / C3 * 100</f>
         <v>6.0439560439560438</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <f>ABS(E3 - C3) / C3 * 100</f>
         <v>4.395604395604396</v>
       </c>
-      <c r="H3">
+      <c r="I3">
         <f>AVERAGE(C3:E3)</f>
         <v>175.66666666666666</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
         <v>14.5</v>
       </c>
@@ -546,16 +552,16 @@
         <v>184</v>
       </c>
       <c r="E4" s="1"/>
-      <c r="F4">
-        <f t="shared" si="0"/>
+      <c r="G4">
+        <f>ABS(D4 - C4) / C4 * 100</f>
         <v>0</v>
       </c>
-      <c r="H4">
-        <f t="shared" ref="H4:H12" si="1">AVERAGE(C4:E4)</f>
+      <c r="I4">
+        <f>AVERAGE(C4:E4)</f>
         <v>184</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <v>16.5</v>
       </c>
@@ -563,18 +569,18 @@
         <v>72</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
-      <c r="F5" t="s">
-        <v>10</v>
-      </c>
-      <c r="H5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="G5" t="s">
+        <v>6</v>
+      </c>
+      <c r="I5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
         <v>21.5</v>
       </c>
@@ -588,16 +594,16 @@
         <v>218</v>
       </c>
       <c r="E6" s="1"/>
-      <c r="F6">
-        <f t="shared" si="0"/>
+      <c r="G6">
+        <f>ABS(D6 - C6) / C6 * 100</f>
         <v>0.92592592592592582</v>
       </c>
-      <c r="H6">
-        <f t="shared" si="1"/>
+      <c r="I6">
+        <f t="shared" ref="I6:I12" si="0">AVERAGE(C6:E6)</f>
         <v>217</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
         <v>29.5</v>
       </c>
@@ -611,16 +617,16 @@
         <v>229</v>
       </c>
       <c r="E7" s="1"/>
-      <c r="F7">
+      <c r="G7">
+        <f>ABS(D7 - C7) / C7 * 100</f>
+        <v>0</v>
+      </c>
+      <c r="I7">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <f t="shared" si="1"/>
         <v>229</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
         <v>34.5</v>
       </c>
@@ -634,15 +640,15 @@
         <v>357</v>
       </c>
       <c r="E8" s="1"/>
-      <c r="F8">
+      <c r="G8">
         <v>0</v>
       </c>
-      <c r="H8">
-        <f t="shared" si="1"/>
+      <c r="I8">
+        <f t="shared" si="0"/>
         <v>357</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" s="2">
         <v>47.5</v>
       </c>
@@ -656,16 +662,16 @@
         <v>258</v>
       </c>
       <c r="E9" s="1"/>
-      <c r="F9">
+      <c r="G9">
+        <f>ABS(D9 - C9) / C9 * 100</f>
+        <v>0.76923076923076927</v>
+      </c>
+      <c r="I9">
         <f t="shared" si="0"/>
-        <v>0.76923076923076927</v>
-      </c>
-      <c r="H9">
-        <f t="shared" si="1"/>
         <v>259</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
         <v>57.5</v>
       </c>
@@ -679,16 +685,16 @@
         <v>310</v>
       </c>
       <c r="E10" s="1"/>
-      <c r="F10">
-        <f t="shared" si="0"/>
+      <c r="G10">
+        <f>ABS(D10 - C10) / C10 * 100</f>
         <v>1.639344262295082</v>
       </c>
-      <c r="H10">
-        <f t="shared" si="1"/>
+      <c r="I10">
+        <f>AVERAGE(C10:D10)</f>
         <v>307.5</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" s="2">
         <v>63</v>
       </c>
@@ -702,16 +708,16 @@
         <v>243</v>
       </c>
       <c r="E11" s="1"/>
-      <c r="F11">
-        <f t="shared" si="0"/>
+      <c r="G11">
+        <f>ABS(D11 - C11) / C11 * 100</f>
         <v>0.81632653061224492</v>
       </c>
-      <c r="H11">
-        <f t="shared" si="1"/>
+      <c r="I11">
+        <f>AVERAGE(C11:E11)</f>
         <v>244</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
         <v>78.5</v>
       </c>
@@ -727,16 +733,16 @@
       <c r="E12" s="1">
         <v>235</v>
       </c>
-      <c r="F12">
-        <f t="shared" si="0"/>
+      <c r="G12">
+        <f>ABS(D12 - C12) / C12 * 100</f>
         <v>5.3278688524590159</v>
       </c>
-      <c r="G12">
+      <c r="H12">
         <f>ABS(E12 - C12) / C12 * 100</f>
         <v>3.6885245901639343</v>
       </c>
-      <c r="H12">
-        <f t="shared" si="1"/>
+      <c r="I12">
+        <f t="shared" si="0"/>
         <v>236.66666666666666</v>
       </c>
     </row>

--- a/data/03-21-densitycutter.xlsx
+++ b/data/03-21-densitycutter.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jille\Documents\Uni\Master-Mechatronik\Masterarbeit\SMP-SignalProcessing\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0879BE1A-EB3F-46B4-9BE2-7429CEE3B3FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EA6C691-2338-4163-BB97-F59FF0128D45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28905" yWindow="60" windowWidth="14610" windowHeight="15585" xr2:uid="{FC14D368-F54E-477D-9C66-9A96069A1AC9}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{FC14D368-F54E-477D-9C66-9A96069A1AC9}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
